--- a/docs/research/provinces/SportsHub-Prince-Edward-Island.xlsx
+++ b/docs/research/provinces/SportsHub-Prince-Edward-Island.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$13</definedName>
@@ -63,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -452,6 +453,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,6 +537,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -562,7 +569,6 @@
           <t>Charlottetown, PE C1A 1B6 (per SportsEngine org listing; no street address published)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>tigersbasketball.ca@gmail.com</t>
@@ -722,13 +728,11 @@
           <t>Practices at Eliot River School, Cornwall PE (no office address published)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>cornwallcomets@gmail.com</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Eric Saindon — association contact per Basketball PEI minor-associations registry (role not stated)</t>
@@ -791,9 +795,6 @@
           <t>Kensington</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>https://www.facebook.com/pages/category/Community/Kensington-Noreasters-Basketball-1665784420326120/</t>
@@ -861,10 +862,6 @@
           <t>Montague (Town of Three Rivers)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Shawn Fraser and Duane Yoshikawa — association contacts per Basketball PEI minor-associations registry (roles not stated)</t>
@@ -927,10 +924,6 @@
           <t>Morell</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Jody Kinney — association contact per Basketball PEI minor-associations registry (role not stated)</t>
@@ -993,9 +986,6 @@
           <t>North Shore region (rural communities north of Charlottetown; exact base town not published)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>http://www.northshoreospreys.ca/</t>
@@ -1063,8 +1053,6 @@
           <t>Souris</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>sourisminorbasketball@gmail.com</t>
@@ -1137,10 +1125,6 @@
           <t>South Shore region (Crapaud/Victoria area; exact base town not published)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Contact listed as VACANT on Basketball PEI minor-associations registry; the registry's contact link points to mconnolly@sportpei.pe.ca (Sport PEI staff, apparent interim contact)</t>
@@ -1203,9 +1187,6 @@
           <t>Stratford</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>http://stratfordfoxes.ca/</t>
@@ -1273,27 +1254,21 @@
           <t>Summerside</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>https://www.facebook.com/bgcsummerside/</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Weekly drop-in youth basketball nights (e.g. Wednesday night basketball) as part of broader youth programming — NOT organized league/rep basketball</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>multi-sport org (youth charity with drop-in basketball)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1331,8 +1306,6 @@
           <t>Summerside</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>epmbasting@hotmail.ca</t>
@@ -1405,10 +1378,6 @@
           <t>West Prince region (Alberton/O'Leary area; exact base town not published)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Joey Smallman — association contact per Basketball PEI minor-associations registry (role not stated)</t>
@@ -1451,7 +1420,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1748,13 +1717,11 @@
           <t>spring-summer circuit</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Charlottetown area</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Spring (April-May window, paired with the Courtside Sneakers boys leagues)</t>
@@ -2808,7 +2775,6 @@
           <t>Charlottetown</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>tigersbasketball.ca@gmail.com</t>
@@ -2868,7 +2834,6 @@
           <t>Cornwall</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>cornwallcomets@gmail.com</t>
@@ -2879,7 +2844,6 @@
           <t>Eric Saindon — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2892,8 +2856,6 @@
           <t>Kensington</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Stacey Kember — association contact per Basketball PEI minor-associations registry (role not stated)</t>
@@ -2916,14 +2878,11 @@
           <t>Montague (Town of Three Rivers)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Shawn Fraser and Duane Yoshikawa — association contacts per Basketball PEI minor-associations registry (roles not stated)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2936,14 +2895,11 @@
           <t>Morell</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Jody Kinney — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2956,8 +2912,6 @@
           <t>North Shore region (rural communities north of Charlottetown; exact base town not published)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Duane Pineau and Lucas Squires — association contacts per Basketball PEI minor-associations registry (roles not stated)</t>
@@ -2980,7 +2934,6 @@
           <t>Souris</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>sourisminorbasketball@gmail.com</t>
@@ -3008,14 +2961,11 @@
           <t>South Shore region (Crapaud/Victoria area; exact base town not published)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Contact listed as VACANT on Basketball PEI minor-associations registry; the registry's contact link points to mconnolly@sportpei.pe.ca (Sport PEI staff, apparent interim contact)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3028,8 +2978,6 @@
           <t>Stratford</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Jason MacDonald — association contact per Basketball PEI minor-associations registry (role not stated)</t>
@@ -3052,7 +3000,6 @@
           <t>Summerside</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>epmbasting@hotmail.ca</t>
@@ -3080,14 +3027,11 @@
           <t>West Prince region (Alberton/O'Leary area; exact base town not published)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Joey Smallman — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F13"/>

--- a/docs/research/provinces/SportsHub-Prince-Edward-Island.xlsx
+++ b/docs/research/provinces/SportsHub-Prince-Edward-Island.xlsx
@@ -439,7 +439,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -469,77 +469,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Owner/Principal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Leagues</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Teams Counted</t>
         </is>
       </c>
     </row>
@@ -554,67 +554,67 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Queens County, PEI</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Charlottetown</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Charlottetown, PE C1A 1B6 (per SportsEngine org listing; no street address published)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>tigersbasketball.ca@gmail.com</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>http://tigersbasketball.ca/</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Jeff Perry — association contact per Basketball PEI minor-associations registry (role not stated; each association governed by its own board/executive)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Minor/mini basketball (elementary ages): house-league minis, Small Ball/Jr. Mini, and mini rep teams; largest association on the Island (Charlottetown)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>GOALLINE (Stack Sports) — tigersbasketball.ca titled 'Powered by GOALLINE'; domain now DNS-dead and goalline.ca sites redirect to stacksports.com (platform sunset). Unclaimed SportsEngine directory listing exists. Active presence is Facebook.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>One of 11 Basketball PEI member minor associations (registry content build Sep 2025). GOALLINE website defunct — org effectively has no working website; competitive-intel: prime candidate for platform replacement.</t>
         </is>
@@ -631,72 +631,72 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Province-wide (PEI)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Charlottetown</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>40 Enman Cres. Room 205, Charlottetown, PE C1A 1E6 (Basketball PEI office, Royalty Centre; postal code also appears as C1E 1E6 in directory listings)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>902-368-4986</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>islandaces@gmail.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/island-aces</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Operated by Basketball PEI (PSO) — Basketball PEI executive director/office is the program owner; no separate club president</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Provincial rep/club program for top players: advanced training, ID camps and tryouts for U12/U13/U14+ boys and girls; seeks highest-level competition within the Maritimes region and beyond</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Regional/Maritime club tournaments and exhibition competition (outside the mapped PEI leagues)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>PSO-run rep club program (nonprofit)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Basketball PEI website runs on Web.com SiteBuilder (mywebsitebuilder); no dedicated registration platform found</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/island-aces</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>The closest thing PEI has to an elite/AAU-style club — run by the PSO itself, not private. No private basketball academies were found anywhere in PEI (searches for academies/private training returned only PSO SuperSkillz camps and UPEI varsity camps, which are excluded).</t>
         </is>
@@ -713,62 +713,62 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Queens County, PEI</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Cornwall</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Practices at Eliot River School, Cornwall PE (no office address published)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>cornwallcomets@gmail.com</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Eric Saindon — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Basketball instruction and games for grades 1-6; season mid-October to March; one weekday practice + Saturdays at Eliot River School (per Town of Cornwall program guide)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>None found — Facebook + email registration (Town of Cornwall guide directs registrants to email in September)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Older cached registry snapshot named Brenda Brydon as contact — superseded by current PSO listing. Do NOT confuse with cornwallbasketball.com / CLS Minor Basketball (Cornwall, Ontario).</t>
         </is>
@@ -785,57 +785,57 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Prince County, PEI</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Kensington</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>https://www.facebook.com/pages/category/Community/Kensington-Noreasters-Basketball-1665784420326120/</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Stacey Kember — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>None found — Facebook-only presence</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>PSO registry hyperlinks contact name to kjgallant@ihis.org — mismatched/likely stale mailto; not treated as the association's email.</t>
         </is>
@@ -852,52 +852,52 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Kings County (Eastern PEI)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Montague (Town of Three Rivers)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Shawn Fraser and Duane Yoshikawa — association contacts per Basketball PEI minor-associations registry (roles not stated)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Minor/mini basketball for the Montague / Three Rivers area: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>None found — no web presence located beyond PSO registry</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Covers the Montague census target (Montague amalgamated into Town of Three Rivers, 2018). Older cached registry snapshot named Juanita Hughes (Montague &amp; Area) — superseded. Do NOT confuse with Three Rivers Youth Basketball League (Michigan, USA) on SportsEngine.</t>
         </is>
@@ -914,52 +914,52 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Kings County (Eastern PEI)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Morell</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Jody Kinney — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>None found — no web presence located beyond PSO registry</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Small rural association; Wildcats branding also on Allstar Cresting youth apparel shop.</t>
         </is>
@@ -976,57 +976,57 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Queens County (North Shore), PEI</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>North Shore region (rural communities north of Charlottetown; exact base town not published)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>http://www.northshoreospreys.ca/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Duane Pineau and Lucas Squires — association contacts per Basketball PEI minor-associations registry (roles not stated)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep ('Minor Basketball Association in Prince Edward Island' per site meta)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Pointstreak Sites — northshoreospreys.ca is a frameset embedding ospreysminorbasketball.pointstreaksites.com; Pointstreak site now dead/blocked (WPEngine 403), so effectively website-less</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Full name on Pointstreak site: 'BPEI: North Shore Minor Basketball Association - Ospreys'. Defunct website — platform-replacement candidate.</t>
         </is>
@@ -1043,62 +1043,62 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Kings County (Eastern PEI)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Souris</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>sourisminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://www.facebook.com/sourisminorbasketball/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>John MacIntosh — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>None found — Facebook-only presence</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Not to be confused with Souris Slammers baseball (Baseball PEI RAMP pages). | enriched 2026-07-18</t>
         </is>
@@ -1115,52 +1115,52 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Queens/Prince County border (South Shore), PEI</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>South Shore region (Crapaud/Victoria area; exact base town not published)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Contact listed as VACANT on Basketball PEI minor-associations registry; the registry's contact link points to mconnolly@sportpei.pe.ca (Sport PEI staff, apparent interim contact)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>None found — no web presence located beyond PSO registry</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Leadership vacancy as of PSO registry content build (Sep 2025) — governance gap; org may be dormant or volunteer-starved.</t>
         </is>
@@ -1177,57 +1177,57 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Queens County, PEI</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Stratford</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>http://stratfordfoxes.ca/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Jason MacDonald — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep; 'Come Try Basketball' intro events at Stratford Town Hall; registration announced via Town of Stratford channels</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>GOALLINE (Stack Sports) — 'Stratford Minor Basketball powered by GOALLINE' at stratfordfoxes.ca / site4994.goalline.ca ('Welcome to the 2024-25 Stratford Minor Basketball Season!'); both now dead (goalline.ca redirects to stacksports.com; stratfordfoxes.ca DNS-dead)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Older cached registry snapshot named Rudi Tersteege as contact — superseded by current PSO listing (Jason MacDonald). Do NOT confuse with stratfordbasketball.com (Stratford, Ontario). Website defunct — platform-replacement candidate.</t>
         </is>
@@ -1244,42 +1244,42 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Prince County, PEI</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Summerside</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>https://www.facebook.com/bgcsummerside/</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Weekly drop-in youth basketball nights (e.g. Wednesday night basketball) as part of broader youth programming — NOT organized league/rep basketball</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>multi-sport org (youth charity with drop-in basketball)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://www.facebook.com/bgcsummerside/posts/-wednesday-night-basketball-is-back-starting-next-week-january-14th-we-will-have/1340845944749839/</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Marginal entry included for completeness — drop-in rec basketball only, not a Basketball PEI member and fields no teams. Low GTM relevance.</t>
         </is>
@@ -1296,62 +1296,62 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Prince County (East Prince), PEI</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Summerside</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>epmbasting@hotmail.ca</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://www.facebook.com/EastPrinceStingBasketball/</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Jennifer Halupa — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Minor/mini basketball for the Summerside / East Prince area: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>None found — Facebook-only presence; former site stingbasketball.ca is dead</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Second email on PSO page: epmba.sting.basketball@gmail.com. Older contact Jason Woods (cached snapshot) superseded. Historic 'Summerside Area Minor Basketball (902) 888-2288' listing appears in a 2013 City of Summerside youth directory — stale, not used. No website — platform candidate.</t>
         </is>
@@ -1368,52 +1368,52 @@
           <t>Prince Edward Island</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Prince County (West Prince), PEI</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>West Prince region (Alberton/O'Leary area; exact base town not published)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Joey Smallman — association contact per Basketball PEI minor-associations registry (role not stated)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Minor/mini basketball: house-league minis and mini rep</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>PEI Mini Rep League; BPEI Jamboree Series + house-league minis</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>None found — no web presence located beyond PSO registry</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://basketballpei.ca/minor-associations</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Westernmost of the 11 member associations.</t>
         </is>
